--- a/Result/checksun_type/冷熱軋鋼板捲.xlsx
+++ b/Result/checksun_type/冷熱軋鋼板捲.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>18.23</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>18.62</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>18.37</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>18.37</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>49420487.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>45464237.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>45464237.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>61433394.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>71181440.54</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>71181440.54000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-12323765.25532388</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>49420487</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>49420487.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>18.09</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>18.36</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>27161770.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>45608850.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>45608850.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>69183329.9</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>71371132.48</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>71371132.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-12565256.02268657</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>27161770</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>27161770.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>18.02</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>18.36</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>41928856.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>67832334.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>67832334.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>89631178.4</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>71708187.66</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>71708187.66</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-10076621.15382306</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>41928856</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>41928856.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>18.12</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>18.36</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>18.36</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>63194242.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>69799901.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>69799901.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>103580462.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>72683928.24</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>72683928.23999999</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-7743736.942810073</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>63194242</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>63194242.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>18.2</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>18.62</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>18.37</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>18.37</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>45615831.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>65756828.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>65756828</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>116944133.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>72905130.54</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>72905130.54000001</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-6412917.393405452</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>45615831</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>45615831.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>18.26</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>18.64</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>18.38</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>18.38</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>50143555.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>77402551.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>77402551.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>133220732.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>72717397.78</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>72717397.78</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-2399312.665920079</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>50143555</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>50143555.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>18.48</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>18.4</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>138279187.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>92757809.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>92757809</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>160505159.0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>74105029.24</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>74105029.23999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>2934984.825699031</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>138279187</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>138279187.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>18.68</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>18.68</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>18.41</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>18.41</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>51766691.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>111430022.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>111430022.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>157838782.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>72727159.8</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>72727159.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>1007485.498522803</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>51766691</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>51766691.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>18.98</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>18.4</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>42978876.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>137361024.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>137361024.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>155442945.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>72324294.6</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>72324294.59999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>7487129.406180963</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>42978876</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>42978876.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>19.27</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>18.63</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>18.39</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>18.39</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>103844447.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>168131438.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>168131438.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>154326038.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>72328381.1</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>72328381.09999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>17417917.688329</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>103844447</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>103844447.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>19.55</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>18.62</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>18.39</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>18.39</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>126919844.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>189038912.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>189038912.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>146183974.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>71007615.98</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>71007615.98</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>24461378.42395729</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>126919844</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>126919844.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>27.24</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>27.4</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>27.55</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>27.55</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>0</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-30.09271433251715</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>0</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>27.28</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>27.4</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>27.56</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>27.56</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>0</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>0</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-30.09271433251715</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>0</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>27.32</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>27.42</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>27.58</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>82.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>0</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>0</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-30.09271433251715</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>82</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>27.36</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>27.44</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>27.58</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>30.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>0</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>0</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-33.0866462288709</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>30</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>27.58</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>27.46</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>27.61</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>27.61</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>112.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>0</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>0</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-30.6105972869166</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>112</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>27.5</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>27.46</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>27.61</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>27.61</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>0</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>0</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-40.06346521364927</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>0</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>27.5</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>27.48</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>27.64</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>27.64</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>0</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>0</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-40.06346521364927</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>0</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>27.5</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>27.51</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>27.66</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>27.66</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>0</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>0</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-40.06346521364927</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>0</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>27.5</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>27.54</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>27.67</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>27.67</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>0</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>0</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-40.06346521364927</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>0</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>27.5</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>27.56</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>27.68</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>27.68</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>0</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>0</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-40.06346521364927</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>0</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>27.5</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>27.56</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>27.68</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>27.68</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>0</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>0</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-40.06346521364927</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>0</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>20.37</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>20.66</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>21.49</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>21.49</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>4480819.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>2684983.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>2684983.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>3918258.0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>3961621.2</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>3961621.2</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-172145.8591817361</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>4480819</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>4480819.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>20.25</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>20.69</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>21.53</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>21.53</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>1595142.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>2530684.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>2530684.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>3784465.0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>4055640.84</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>4055640.84</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-299650.3108149092</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>1595142</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>1595142.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>20.2</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>20.74</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>21.58</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>21.58</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>2404984.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>4151334.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>4151334</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>4020289.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>4111178.46</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>4111178.46</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-161918.0520474804</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>2404984</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>2404984.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>20.21</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>20.81</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>21.62</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>21.62</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>1676871.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>5082092.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>5082092.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>4286330.1</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>4209756.2</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>4209756.2</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-46143.68052088609</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>1676871</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>1676871.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>20.3</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>20.89</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>21.67</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>21.67</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>3267102.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>5456414.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>5456414.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>4586333.1</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>4251651.02</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>4251651.02</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>198908.3745357078</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>3267102</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>3267102.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>20.42</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>20.96</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>21.72</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>21.72</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>3709325.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>5151532.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>5151532.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>4729296.5</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>4240100.04</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>4240100.04</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>371496.9755259957</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>3709325</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>3709325.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>20.59</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>21.04</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>21.78</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>9698388.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>5038245.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>5038245.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>4586340.3</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>4205912.6</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>4205912.6</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>557403.334957622</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>9698388</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>9698388.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>20.72</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>21.14</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>21.83</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>21.83</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>7058775.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>3889244.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>3889244.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>3797532.8</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>4053124.84</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>4053124.84</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>161391.2650400284</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>7058775</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>7058775.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>20.78</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>21.21</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>21.87</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>21.87</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>3548481.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>3490568.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>3490568</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>3318934.5</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>4038361.46</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>4038361.46</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-127288.5585936764</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>3548481</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>3548481.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>20.78</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>21.28</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>21.91</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>21.91</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>1742693.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>3716252.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>3716252</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>3089728.1</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>4062428.44</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>4062428.44</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-159039.358120624</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>1742693</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>1742693.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>20.76</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>21.32</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>21.95</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>3142889.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>4307060.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>4307060.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>3085047.2</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>4105367.42</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>4105367.42</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-5240.38036909746</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>3142889</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>3142889.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>14.77</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>14.76</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>14.98</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>14.98</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>21390072.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>17745633.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>17745633.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>22336867.7</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>21605157.3</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>21605157.3</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-885753.319650773</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>21390072</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>21390072.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>14.71</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>14.75</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>14.99</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>6035022.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>17347726.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>17347726.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>21252785.0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>21456486.66</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>21456486.66</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-1121042.596709423</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>6035022</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>6035022.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>14.69</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>14.75</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>15</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>29654089.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>22978020.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>22978020</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>24880422.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>21703786.6</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>21703786.6</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>228051.0288035572</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>29654089</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>29654089.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>14.63</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>14.76</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>15</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>19913233.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>26399559.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>26399559.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>23898027.4</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>21326734.56</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>21326734.56</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-383431.3643494621</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>19913233</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>19913233.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>14.65</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>14.76</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>15.01</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>11735751.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>25646918.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>25646918.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>22780299.1</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>21256435.2</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>21256435.2</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-199620.5201270096</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>11735751</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>11735751.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,21 +17397,17 @@
           <t>14.67</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>14.77</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
+      <c r="AM40" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="AO40" t="inlineStr">
         <is>
           <t>15.02</t>
         </is>
       </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
-      </c>
       <c r="AP40" t="inlineStr">
         <is>
           <t>-6.12</t>
@@ -17680,20 +17448,16 @@
           <t>19400538.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>26928102.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>26928102</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>22606324.4</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>21239084.18</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>21239084.18</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>946254.490195319</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>19400538</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>19400538.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,21 +17827,17 @@
           <t>14.7</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>14.78</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
+      <c r="AM41" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="AO41" t="inlineStr">
         <is>
           <t>15.03</t>
         </is>
       </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
-      </c>
       <c r="AP41" t="inlineStr">
         <is>
           <t>-8.55</t>
@@ -18116,20 +17878,16 @@
           <t>34186489.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>25157843.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>25157843.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>22136311.8</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>21067782.38</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>21067782.38</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>1728196.808863096</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>34186489</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>34186489.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,21 +18257,17 @@
           <t>14.71</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>14.78</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
+      <c r="AM42" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="AO42" t="inlineStr">
         <is>
           <t>15.04</t>
         </is>
       </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
       <c r="AP42" t="inlineStr">
         <is>
           <t>-10.33</t>
@@ -18552,20 +18308,16 @@
           <t>46761786.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>26782825.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>26782825.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>21400574.0</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>20605966.7</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>20605966.7</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>1199326.913786244</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>46761786</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>46761786.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>14.78</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>14.81</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>15.06</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>16150030.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>21396495.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>21396495.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>18997826.0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>19984793.34</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>19984793.34</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-946387.8618159145</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>16150030</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>16150030.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>14.78</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>14.81</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>15.06</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>18141667.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>19913679.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>19913679.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>21992819.6</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>19877828.98</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>19877828.98</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-698064.1176112816</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>18141667</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>18141667.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>14.78</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>14.81</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>15.07</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>15.07</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>10549245.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>18284546.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>18284546.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>21879346.6</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>19739963.26</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>19739963.26</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-531774.7288328297</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>10549245</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>10549245.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>14.49</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>14.55</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>15.23</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>15.23</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>122168820.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>55877303.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>55877303.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>50099375.9</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>59366944.36</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>59366944.36</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>4085064.155979253</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>122168820</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>122168820.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>14.26</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>14.54</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>15.24</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>15.24</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>29289673.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>37332423.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>37332423.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>41294690.4</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>58747134.16</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>58747134.16</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-2418366.581848741</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>29289673</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>29289673.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>14.18</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>14.58</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>15.26</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>15.26</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>56373070.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>38065328.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>38065328.6</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>42507010.0</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>59897788.2</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>59897788.2</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-1671274.507965557</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>56373070</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>56373070.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>14.22</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>14.64</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>15.29</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>42160227.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>33319286.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>33319286.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>39386768.9</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>59943683.6</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>59943683.6</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-3446104.277133673</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>42160227</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>42160227.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>14.39</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>14.71</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>15.32</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>15.32</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>29394728.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>36082103.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>36082103</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>36726915.8</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>60196307.34</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>60196307.34</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-4335695.616047643</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>29394728</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>29394728.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>14.52</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>14.78</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>15.35</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>15.35</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>29444419.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>44321448.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>44321448.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>36990831.2</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>61119707.72</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>61119707.72</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-4083962.078208745</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>29444419</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>29444419.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>14.6</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>14.86</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>15.39</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>32954199.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>45256957.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>45256957.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>36579452.4</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>62794805.98</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>62794805.98</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-3583810.985645726</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>32954199</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>32954199.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>14.6</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>15.42</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>15.42</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>32642859.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>46948691.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>46948691.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>38146731.5</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>62991916.04</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>62991916.04</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-3117364.032496922</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>32642859</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>32642859.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>14.57</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>15.45</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>55974310.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>45454251.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>45454251.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>39491259.0</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>64102186.58</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>64102186.58</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-2306318.95540946</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>55974310</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>55974310.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>14.53</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>15.48</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>15.48</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>70591454.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>37371728.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>37371728.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>40590135.2</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>65990743.12</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>65990743.12</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-3565112.918305591</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>70591454</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>70591454.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>14.52</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>15.07</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>15.5</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>15.5</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>34121965.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>29660214.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>29660214.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>40310844.1</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>65986839.24</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>65986839.24</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-6802187.118217729</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>34121965</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>34121965.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>20.02</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>19.78</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>19.94</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>19.94</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>26219629.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>16889576.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>16889576</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>17236189.3</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>20277790.28</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>20277790.28</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-302881.9023336619</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>26219629</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>26219629.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>19.89</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>19.73</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>19.94</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>19.94</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>17532722.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>14859100.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>14859100</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>16642108.4</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>20371841.18</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>20371841.18</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-1128834.726736229</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>17532722</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>17532722.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>19.84</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>19.95</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>11740057.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>16014559.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>16014559.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>16278001.2</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>20292426.12</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>20292426.12</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-1337711.771356456</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>11740057</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>11740057.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>19.82</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>19.67</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>19.96</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>19.96</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>18789662.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>18102005.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>18102005</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>17635266.7</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>20278770.0</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>20278770</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-967689.4504083358</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>18789662</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>18789662.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>19.89</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>19.97</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>19.97</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>10165810.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>17346115.8</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>17346115.8</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>24061820.1</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>20181907.52</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>20181907.52</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-1159840.618682154</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>10165810</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>10165810.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>19.94</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>19.97</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>19.97</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>16067249.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>17582802.6</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>17582802.6</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>24285645.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>20299032.42</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>20299032.42</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-468935.2655489594</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>16067249</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>16067249.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>20.06</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>19.64</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>19.99</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>23310018.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>18425116.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>18425116.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>24110880.8</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>20453854.52</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>20453854.52</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-97476.96587479487</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>23310018</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>23310018.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>20.1</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>19.62</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>20</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>22177286.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>16541443.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>16541443.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>23454311.7</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>20348159.38</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>20348159.38</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-339351.8961304575</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>22177286</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>22177286.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>20.13</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>20</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>15010216.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>17168528.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>17168528.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>22516228.9</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>20143353.8</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>20143353.8</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-551403.6573481709</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>15010216</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>15010216.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>20.17</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>19.57</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>20.01</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>20.01</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>11349244.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>30777524.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>30777524.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>22335947.5</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>20370385.8</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>20370385.8</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-66741.39989675581</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>11349244</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>11349244.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>20.05</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>19.55</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>20.02</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>20278820.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>30988489.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>30988489</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>22686745.2</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>20671912.34</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>20671912.34</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>1020263.875030149</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>20278820</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>20278820.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>38.45</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>40.06</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>39.56</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>39.56</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>73174356.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>58664208.6</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>58664208.6</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>113166126.2</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>324096761.4</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>324096761.4</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-28930821.26491457</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>73174356</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>73174356.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>38.02</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>40.17</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>39.43</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>39.43</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>62952000.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>59780231.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>59780231.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>112394101.7</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>323520164.9</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>323520164.9</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-31679204.94081365</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>62952000</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>62952000.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>37.88</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>40.34</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>39.32</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>39.32</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>38873667.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>67678135.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>67678135.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>117472784.5</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>323016080.82</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>323016080.82</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-33378814.72992612</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>38873667</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>38873667.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>38.11</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>40.55</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>39.23</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>39.23</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>61784640.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>104240622.0</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>104240622</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>120854370.0</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>322984917.42</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>322984917.42</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-32034906.7954466</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>61784640</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>61784640.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>39.04</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>40.7</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>39.16</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>39.16</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>56536380.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>117749281.6</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>117749281.6</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>119454440.1</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>323049284.24</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>323049284.24</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-31425681.61063847</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>56536380</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>56536380.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>39.9</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>40.78</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>39.09</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>40.78</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>39.09</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>78754470.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>167668043.8</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>167668043.8</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>120880868.6</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>323291004.72</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>323291004.72</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-28870700.57481831</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>78754470</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>78754470.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>40.61</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>40.96</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>39.04</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>40.96</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>39.04</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>102441519.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>165007972.0</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>165007972</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>124267924.0</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>322788664.2</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>322788664.2</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-26570140.86026031</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>102441519</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>102441519.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>41.26000000000001</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>41.14</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>38.97</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>38.97</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>221686101.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>167267433.8</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>167267433.8</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>127655393.9</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>322735086.18</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>322735086.18</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-24872591.48731101</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>221686101</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>221686101.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>41.53</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>41.2</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>38.87</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>38.87</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>129327938.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>137468118.0</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>137468118</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>114822784.7</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>319007700.52</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>319007700.52</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-34335419.32997948</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>129327938</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>129327938.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>41.14</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>41.16</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>38.72</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>38.72</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>306130191.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>121159598.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>121159598.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>115700657.9</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>317274681.72</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>317274681.72</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-36731962.37914947</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>306130191</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>306130191.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>40.66</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>41.04</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>38.54</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>38.54</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>65454111.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>74093693.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>74093693.40000001</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>151075791.9</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>311916081.02</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>311916081.02</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-57786838.04299413</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>65454111</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>65454111.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>27.85</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>27.32</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>27.32</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>922889.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>405378.6</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>405378.6</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>562072.0</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>418350.92</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>418350.92</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>21506.4770962398</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>922889</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>922889.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>28.1</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>27.76</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>27.26</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>27.26</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>434795.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>325239.0</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>325239</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>528479.1</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>428076.44</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>428076.44</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-17026.39684747037</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>434795</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>434795.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>27.96</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>27.22</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>27.22</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>280586.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>352472.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>352472</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>533293.3</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>422026.78</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>422026.78</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-19169.48830821813</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>280586</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>280586.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>27.88</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>27.66</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>27.19</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>27.19</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>238141.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>642925.8</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>642925.8</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>519276.8</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>425600.48</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>425600.48</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-5024.030098278541</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>238141</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>238141.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>27.86</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>27.63</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>27.16</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>27.16</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>150482.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>701389.6</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>701389.6</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>531653.6</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>436635.56</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>436635.56</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>19910.87556228798</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>150482</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>150482.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>27.78</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>27.12</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>27.12</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>522191.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>718765.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>718765.4</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>569184.6</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>457466.5</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>457466.5</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>64213.10237872985</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>522191</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>522191.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>27.76</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>27.54</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>27.07</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>27.07</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>570960.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>731719.2</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>731719.2</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>564833.7</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>448558.68</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>448558.68</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>85382.70846012083</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>570960</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>570960.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>27.73</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>27.5</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>27.03</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>27.03</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>1732855.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>714114.6</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>714114.6</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>569415.9</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>441124.92</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>441124.92</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>107350.3704171036</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>1732855</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>1732855.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>27.73</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>27.47</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>26.98</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>26.98</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>530460.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>395627.8</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>395627.8</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>451171.5</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>411292.72</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>411292.72</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>10410.05284075369</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>530460</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>530460.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>27.76</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>27.44</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>26.93</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>26.93</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>237361.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>361917.6</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>361917.6</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>409681.8</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>406819.52</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>406819.52</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>380.1329873698996</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>237361</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>237361.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>27.73</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>26.88</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>26.88</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>586960.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>419603.8</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>419603.8</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>470592.1</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>416157.3</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>416157.3</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>17441.5641615584</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>586960</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>586960.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>17.88</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>18.08</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>18.7</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>554883691.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>592834457.2</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>592834457.2</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>564016344.7</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>472987580.06</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>472987580.06</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>25737807.48307288</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>554883691</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>554883691.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>17.79</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>18.11</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>18.72</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>18.72</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>421676243.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>575373921.0</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>575373921</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>551015361.7</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>476205258.64</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>476205258.64</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>30387017.07643664</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>421676243</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>421676243.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>17.78</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>18.17</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>18.76</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>18.76</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>1065633753.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>598121428.6</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>598121428.6</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>546982182.2</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>478593233.36</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>478593233.36</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>50215721.02851224</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>1065633753</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>1065633753.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>17.76</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>18.22</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>18.78</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>18.78</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>536795375.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>503700111.2</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>503700111.2</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>483479858.9</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>467113671.08</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>467113671.08</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>7753574.851887524</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>536795375</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>536795375.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>17.83</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>18.28</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>18.82</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>18.82</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>385183224.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>503682309.0</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>503682309</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>465278163.2</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>465379679.6</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>465379679.6</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>3477707.42628485</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>385183224</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>385183224.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>17.89</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>18.33</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>18.86</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>467581010.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>535198232.2</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>535198232.2</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>470575950.6</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>471154088.28</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>471154088.28</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>13489280.58877087</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>467581010</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>467581010.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>17.98</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>18.39</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>18.9</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>535413781.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>526656802.4</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>526656802.4</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>479649025.7</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>491243503.42</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>491243503.42</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>18481433.7284376</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>535413781</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>535413781.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>18.06</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>18.44</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>18.94</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>18.94</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>593527166.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>495842935.8</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>495842935.8</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>491705728.4</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>497565983.76</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>497565983.76</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>17685232.97337449</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>593527166</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>593527166.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>18.1</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>18.5</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>18.98</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>536706364.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>463259606.6</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>463259606.6</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>488073283.7</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>492693666.56</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>492693666.56</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>9689753.752806664</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>536706364</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>536706364.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>18.14</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>18.54</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>19.02</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>542762840.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>426874017.4</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>426874017.4</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>478988131.4</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>492160264.26</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>492160264.26</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>4009521.017966688</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>542762840</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>542762840.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>18.18</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>18.57</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>19.06</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>424873861.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>405953669.0</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>405953669</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>456595423.7</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>492268791.98</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>492268791.98</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-4897202.496732056</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>424873861</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>424873861.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
